--- a/data/ams_weekly_data/White_Mulberry/ads_report_week14.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week14.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Week 14\Week 14\ams_weekly_data\White_Mulberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F3C468-FDE0-4422-B812-3B3DE4AF0B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week14.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week14.xlsx
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2326.5</v>
+        <v>2326</v>
       </c>
       <c r="E2" t="n">
         <v>72</v>
@@ -4254,7 +4254,7 @@
         <v>3537.71</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2326.5</v>
+        <v>2326</v>
       </c>
       <c r="E3" t="n">
         <v>72</v>
@@ -4287,7 +4287,7 @@
         <v>3537.71</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week14.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week14.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
